--- a/Result/checksun_type/臨床實驗、移植技術、疾病治療.xlsx
+++ b/Result/checksun_type/臨床實驗、移植技術、疾病治療.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>27.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>27.32</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>28.96</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>6377966.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>6176987.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>6176987.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5819335.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7057711.28</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7057711.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>318810.7876168946</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>6377966</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>6377966.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>26.65</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>27.34</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>29</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>14065095.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>5502534.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>5502534.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5577139.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7141675.4</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7141675.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>354777.3309102692</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>14065095</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>14065095.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>26.32</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>27.38</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29.06</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2914289.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3848013.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3848013.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>4769960.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7033263.38</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7033263.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-430133.4762031334</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2914289</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2914289.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>26.41</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>27.52</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>29.16</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4874674.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4326733.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4326733.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5162658.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7253837.46</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7253837.46</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-341343.5050721681</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4874674</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4874674.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>26.76</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>29.27</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>29.27</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>2652914.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4882698.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4882698.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5090432.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7327974.3</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7327974.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-412351.0997039247</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>2652914</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2652914.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>26.91</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>27.88</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>29.36</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>29.36</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3005699.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>5461683.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>5461683</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>5213400.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>7669422.94</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>7669422.94</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-261017.9813312953</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3005699</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3005699.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>27.11</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>29.48</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>29.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5792491.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>5651744.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>5651744.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5390737.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>7832741.84</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>7832741.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-73304.13432285003</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5792491</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5792491.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>29.6</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>5307889.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>5691908.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>5691908</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>5278991.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>8214914.5</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>8214914.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-101108.3480849694</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>5307889</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>5307889.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>27.29</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>29.72</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>29.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>7654500.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>5998583.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>5998583.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4953026.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>8631788.52</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>8631788.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-85295.99817067571</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>7654500</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>7654500.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>27.27</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>29.8</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>5547836.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>5298166.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>5298166.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4494096.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>8670075.9</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>8670075.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-311083.2483584471</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>5547836</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>5547836.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>27.34</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>28.52</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>29.89</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>29.89</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>3956007.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4965118.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4965118.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>4940124.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>8893843.2</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>8893843.199999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-396812.3468996035</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>3956007</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3956007.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>74.62</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>70.12</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>75.44</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>75.44</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>11803273.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>5974358.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>5974358</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>4611286.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>5891570.66</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>5891570.66</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>859958.0196654936</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>11803273</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>11803273.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>72.58000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>69.47</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>75.39</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>69.47</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>75.39</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>8218048.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>4055045.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>4055045.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>3547077.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5682855.9</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>5682855.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>323791.1767962705</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>8218048</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>8218048.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>70.92</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>68.88</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>5892899.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2922071.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2922071.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2881353.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>5559272.96</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>5559272.96</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-69594.17647391511</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>5892899</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>5892899.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>70.53999999999999</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>68.68</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>75.53</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>68.68000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>75.53</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1574352.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>2303865.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>2303865.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2493228.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5477122.58</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>5477122.58</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-379964.6391286822</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1574352</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1574352.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>70.47999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>68.61</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>75.66</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>75.66</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2383218.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>2554543.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>2554543.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2423350.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5475035.54</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5475035.54</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-347079.384380897</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2383218</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2383218.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>70.5</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>68.57</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>75.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2206711.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>3248215.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>3248215</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>2398454.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5474171.38</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5474171.38</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-374368.971013315</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2206711</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2206711.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>69.78</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>68.56</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>75.95</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>68.56</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>75.95</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>2553178.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>3039109.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>3039109.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>2377470.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5460980.24</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5460980.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-381072.310094865</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>2553178</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2553178.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>68.96000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>68.54</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>76.09</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>68.54000000000001</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>76.09</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>2801867.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2840636.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>2840636.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2238981.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5451442.24</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5451442.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-414160.247707977</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>2801867</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2801867.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>68.34</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>68.55</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>76.24</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>76.23999999999999</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>2827743.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2682591.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2682591.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>2103125.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5454723.16</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5454723.16</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-473282.5425942801</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>2827743</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2827743.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>67.86</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>68.54</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>76.37</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>68.54000000000001</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>76.37</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>5851576.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2292158.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2292158.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1923889.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5440870.28</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5440870.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-543612.4444820606</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>5851576</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>5851576.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>67.3</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>68.9</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>76.48</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>76.48</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1161182.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1548693.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1548693.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1818036.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>5348507.92</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>5348507.92</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-948651.1098759589</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1161182</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1161182.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>168.6</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>163.72</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>167.16</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>163.72</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>167.16</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>39044.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>41837.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>41837.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>38891.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>1683.46524333056</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>39044</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>39044.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>167.6</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>163.32</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>167.02</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>167.02</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>41554.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>41392.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>41392</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>36289.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>2047.507224716806</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>41554</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>41554.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>166.6</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>162.93</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>166.84</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>162.93</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>166.84</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>83550.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>42576.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>42576</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>34618.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>2225.513368671556</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>83550</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>83550.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>165.4</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>162.55</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>166.67</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>162.55</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>166.67</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>20153.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>32663.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>32663.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>29235.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-2099.246188845646</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>20153</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>20153.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>165.4</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>162.48</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>166.56</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>162.48</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>166.56</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>24885.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>34878.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>34878.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>30090.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-1409.96533569715</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>24885</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>24885.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>164.9</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>162.52</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>166.41</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>166.41</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>36818.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>35944.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>35944.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>28638.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-881.9224977815466</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>36818</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>36818.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>164.2</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>162.65</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>166.25</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>162.65</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>166.25</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>47474.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>31186.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>31186.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>27910.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1374.614068695628</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>47474</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>47474.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>163.0</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>162.65</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>166.09</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>162.65</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>166.09</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>33988.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>26660.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>26660</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>29079.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-3171.080096119476</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>33988</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>33988.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>161.7</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>162.62</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>165.94</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>162.62</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>165.94</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>31229.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>25807.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>25807.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>27476.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-4179.278703292122</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>31229</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>31229.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>160.6</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>162.55</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>165.76</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>162.55</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>165.76</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>30215.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>25302.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>25302.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>26355.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-5174.695331278326</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>30215</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>30215.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>160.3</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>162.57</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>165.63</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>162.57</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>165.63</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>13026.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>21332.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>21332.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>26480.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-6303.265680855824</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>13026</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>13026.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>30.96</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>32.18</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>466.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>222.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>222</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>155.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>7.399020592575255</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>466</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>466.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>31.12</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>31.3</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>32.24</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>32.24</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>346.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>160</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>183.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>0</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-15.23947449555408</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>346</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>346.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>31.13</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>31.37</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>32.26</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>31.37</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>32.26</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>100.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>100.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>166.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>0</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-34.17877196089759</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>69</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>31.08</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>31.42</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>32.31</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>32.31</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>99.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>113.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>113.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>252.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>0</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-30.33566934135624</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>99</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>31.09</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>31.45</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>32.36</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>32.36</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>130.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>94.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>94.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>261.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>0</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-26.97639169410587</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>130</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>31.17</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>32.39</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>32.39</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>156.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>88.8</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>88.8</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>271.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>0</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-24.53540963753014</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>156</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>31.2</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>31.53</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>32.42</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>32.42</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>47.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>207.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>207.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>309.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>0</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-22.95774206965302</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>47</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>31.16</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>32.42</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>32.42</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>134.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>232.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>232.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>324.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>0</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-8.205440470198084</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>134</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>31.12</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>31.67</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>32.44</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>32.44</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>7.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>391.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>391.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>337.2</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>0</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>3.840898974387471</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>7</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>31.15</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>31.74</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>32.47</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>428.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>428.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>368.9</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>0</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>34.51992321756734</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>100</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>31.16</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>31.81</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>32.49</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>32.49</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>751.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>454.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>454.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>372.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>0</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>67.1499605929111</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>751</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>751.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>31.34</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>34.44</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>34.44</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>14400606.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>16708999.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>16708999.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>17597940.1</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>19958818.04</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>19958818.04</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-1023993.381402284</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>14400606</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>14400606.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>29.6</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>31.59</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>34.58</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>34.58</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>15845442.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>17395810.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>17395810</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>18516520.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>20220332.68</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>20220332.68</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-767629.0580196343</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>15845442</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>15845442.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>29.36</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>31.84</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>34.75</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>34.75</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>25554096.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>17488447.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>17488447.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>19781981.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>20394240.98</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>20394240.98</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-528782.8439722881</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>25554096</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>25554096.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>29.32</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>32.13</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>34.93</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>34.93</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>18279821.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>17140007.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>17140007.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>19425353.8</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>20285934.62</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>20285934.62</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-1208901.793762781</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>18279821</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>18279821.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>29.48</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>35.11</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>35.11</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>9465033.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>17451843.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>17451843.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>22266503.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>20288676.86</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>20288676.86</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-1357938.622257672</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>9465033</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>9465033.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>29.75</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>32.85</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>35.29</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>35.29</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>17834658.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>18486880.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>18486880.6</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>23680792.2</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>20484794.4</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>20484794.4</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-577908.9978840277</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>17834658</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>17834658.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>30.21</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>35.48</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>35.48</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>16308631.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>19637231.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>19637231</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>23786251.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>20594420.08</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>20594420.08</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-339686.8917115368</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>16308631</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>16308631.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>30.49</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>33.52</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>35.66</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>35.66</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>23811896.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>22075514.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>22075514.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>24167834.5</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>20696919.56</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>20696919.56</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>176264.9703817256</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>23811896</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>23811896.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>30.73</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>33.83</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>35.82</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>35.82</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>19838998.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>21710699.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>21710699.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>24249994.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>20850248.7</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>20850248.7</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>103122.6315727495</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>19838998</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>19838998.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>31.12</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>34.12</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>35.97</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>35.97</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>14640220.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>27081163.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>27081163</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>25889584.8</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>21528612.2</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>21528612.2</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>420618.2678609006</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>14640220</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>14640220.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>31.68</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>34.37</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>36.14</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>36.14</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>23586410.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>28874703.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>28874703.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>26344919.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>22348666.5</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>22348666.5</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>1416173.310134653</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>23586410</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>23586410.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>14.67</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>16.85</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>1877.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1612.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1612.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1484.9</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>2404.96</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>2404.96</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-218.5414979881389</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1877</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1877.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>14.69</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>15.54</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>16.91</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>1133.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1407.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1407.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1535.1</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>2509.52</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>2509.52</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-260.0078192599899</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>1133</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>1133.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>14.77</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>15.65</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>17</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>2840.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1448.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1448.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1659.6</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>2535.26</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>2535.26</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-230.2451418176345</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>2840</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>2840.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>15.79</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>17.09</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1469.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1343.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1343.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>2211.1</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>2531.16</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>2531.16</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-362.3968475493537</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1469</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1469.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>15.05</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>15.94</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>17.18</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>17.18</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>742.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1287.6</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1287.6</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>2279.5</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>2582.94</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>2582.94</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-391.3493968964758</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>742</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>742.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>15.14</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>16.06</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>17.26</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>17.26</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>852.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1357.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1357.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>2336.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>2620.3</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>2620.3</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-340.8405603603476</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>852</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>852.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>15.33</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>16.18</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>17.34</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>17.34</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>1339.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>1663.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>1663</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>2457.2</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>2719.2</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>2719.2</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-268.297916724438</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>1339</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>1339.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>15.42</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>17.43</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>2315.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>1870.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>1870.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>2981.8</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2774.36</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2774.36</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-207.2620716472657</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>2315</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>2315.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>15.44</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>16.44</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>17.52</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>17.52</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>1190.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>3078.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>3078.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>2915.3</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2807.38</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2807.38</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-217.2372189781881</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>1190</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>1190.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>15.56</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>16.57</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>17.59</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>17.59</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1092.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>3271.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>3271.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>2994.1</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2855.18</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2855.18</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-103.1932430588572</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1092</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1092.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>15.68</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>16.69</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>17.67</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>2379.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>3316.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>3316</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>3207.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2889.22</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2889.22</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>73.91219550657479</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>2379</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>2379.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>46.87</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>46.9</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>46.03</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>46.03</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>11091.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>6300.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>6300.4</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>19121.4</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>7530.12</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>7530.12</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-1059.617506139526</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>11091</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>11091.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>47.02</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>46.9</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>45.99</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>45.99</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>10978.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>4600.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>4600.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>19295.0</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>7344.66</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>7344.66</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-1265.97646289224</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>10978</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>10978.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>47.16</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>46.9</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>45.94</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>45.94</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>3321.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>3373.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>3373</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>18396.2</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>7173.02</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>7173.02</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-1503.454384578537</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>3321</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>3321.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>47.66</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>46.9</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>45.91</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>45.91</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1321.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>5430.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>5430.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>19173.1</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>7113.68</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>7113.68</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-968.6209018240152</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1321</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1321.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>47.95999999999999</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>46.87</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>45.85</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>45.85</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>4791.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>7636.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>7636.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>19825.7</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>7116.7</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>7116.7</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>44.30624860473108</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>4791</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>4791.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>48.36</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>46.76</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>45.79</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>45.79</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>2591.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>31942.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>31942.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>19640.9</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>7056.62</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>7056.62</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>1117.976954624202</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>2591</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>2591.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>48.56</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>45.74</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>45.74</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>4841.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>33989.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>33989.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>21305.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>7043.9</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>7043.9</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>2847.578786272581</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>4841</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>4841.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>48.32000000000001</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>46.56</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>45.7</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>45.7</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>13607.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>33419.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>33419.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>21431.6</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>6976.42</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>6976.42</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>4975.667874831957</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>13607</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>13607.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>47.92</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>46.42</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>45.65</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>45.65</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>12351.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>32916.0</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>32916</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>20317.8</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>6793.3</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>6793.3</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>6898.878434387068</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>12351</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>12351.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>47.45</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>46.28</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>45.56</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>46.28</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>45.56</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>126322.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>32015.2</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>32015.2</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>19423.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>6591.46</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>6591.46</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>9534.505003951974</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>126322</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>126322.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>46.69</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>46.03</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>45.44</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>45.44</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>12827.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>7339.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>7339.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>7286.0</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>4144.24</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>4144.24</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>747.9892103321299</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>12827</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>12827.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>33.55</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>33.66</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>33.7</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>449.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>198.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>198</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>342.1</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>648.24</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>648.24</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-99.91375250760319</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>449</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>449.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>33.55</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>33.7</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>189.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>171.4</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>171.4</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>342.5</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>658.3</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>658.3</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-122.0572889385211</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>189</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>33.53</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>33.72</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>33.71</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>33.72</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>33.71</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>16.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>279.8</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>279.8</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>436.6</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>672.84</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>672.84</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-121.4745806634568</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>16</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>33.49</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>33.74</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>33.71</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>33.71</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>182.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>455.6</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>455.6</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>829.8</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>684.42</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>684.42</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-97.7680481039556</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>182</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>182.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>33.49</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>33.76</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>33.7</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>154.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>462.8</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>462.8</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>857.2</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>700.26</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>700.26</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-78.19557130095552</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>154</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>33.5</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>33.76</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>33.7</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>316.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>486.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>486.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>887.4</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>726.46</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>726.46</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-44.44219117877833</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>316</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>316.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>33.58</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>33.77</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>731.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>513.6</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>513.6</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>873.6</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>726.92</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>726.92</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-11.99299846214046</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>731</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>731.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>33.69</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>33.79</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>895.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>593.4</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>593.4</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>836.3</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>719.78</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>719.78</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-9.672973207581322</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>895</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>895.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>33.65</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>33.68</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>33.68</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>218.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>1204.0</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>1204</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>799.6</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>726.32</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>726.3200000000001</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-23.58461665794027</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>218</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>218.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>33.64</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>33.66</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>33.66</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>271.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>1251.6</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>1251.6</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>815.5</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>734.54</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>734.54</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>29.9196290079019</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>271</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>271.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>33.68</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>33.65</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>453.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1288.6</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1288.6</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>887.6</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>771.24</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>771.24</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>99.60713606596562</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>453</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>453.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>93.2</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>97.23</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>88.79</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>97.23</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>88.79000000000001</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>42037.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>25842.4</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>25842.4</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>56552.8</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>67934.28</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>67934.28</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-12135.08012647409</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>42037</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>42037.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>92.52</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>97.38</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>88.56</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>88.56</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>12382.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>38343.8</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>38343.8</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>56557.5</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>68309.54</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>68309.53999999999</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-13508.89251978778</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>12382</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>12382.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>93.7</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>97.24</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>88.43</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>97.23999999999999</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>88.43000000000001</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>16189.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>48240.6</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>48240.6</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>58792.3</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>69435.04</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>69435.03999999999</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-11811.69977738634</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>16189</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>16189.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>95.17999999999999</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>97.23</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>88.33</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>97.23</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>88.33</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>25530.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>57684.6</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>57684.6</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>62660.2</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>71866.54</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>71866.53999999999</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-9373.185153334773</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>25530</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>25530.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>97.4</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>97.24</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>88.22</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>97.23999999999999</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>88.22</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>33074.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>79687.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>79687</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>67828.1</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>73665.88</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>73665.88</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-6555.657649213419</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>33074</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>33074.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>98.49999999999999</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>97.14</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>87.93</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>87.93000000000001</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>104544.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>87263.2</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>87263.2</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>71316.0</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>74110.96</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>74110.96000000001</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-3104.773441568163</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>104544</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>104544.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>98.88</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>96.76</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>87.62</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>87.62</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>61866.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>74771.2</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>74771.2</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>69626.9</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>72209.06</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>72209.06</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-5721.554093447514</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>61866</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>61866.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>97.88000000000001</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>96.01</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>87.2</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>96.01000000000001</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>87.2</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>63409.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>69344.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>69344</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>71704.0</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>71598.78</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>71598.78</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-4682.828092794865</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>63409</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>63409.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>96.7</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>95.31</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>86.75</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>86.75</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>135542.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>67635.8</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>67635.8</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>79409.8</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>70847.3</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>70847.3</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-3197.0113742627</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>135542</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>135542.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>95.24</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>94.24</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>86.23</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>86.23</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>70955.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>55969.2</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>55969.2</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>91411.3</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>68593.44</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>68593.44</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-8688.772798707374</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>70955</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>70955.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>95.35999999999999</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>93.3</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>85.78</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>85.78</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>42084.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>55368.8</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>55368.8</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>120243.6</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>67557.38</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>67557.38</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-9303.7972336745</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>42084</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>42084.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
